--- a/ig/ch-core/StructureDefinition-ch-core-medicationstatement.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-medicationstatement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="285">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -480,6 +480,19 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>MedicationStatement.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>MedicationStatement.modifierExtension</t>
@@ -1211,12 +1224,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.7890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.2109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2402,43 +2415,41 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -2486,7 +2497,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2495,7 +2506,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -2515,14 +2526,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2535,24 +2546,26 @@
         <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -2600,7 +2613,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2612,16 +2625,16 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>79</v>
@@ -2629,10 +2642,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2655,18 +2668,18 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>79</v>
       </c>
@@ -2714,7 +2727,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2729,13 +2742,13 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>79</v>
@@ -2743,10 +2756,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2769,17 +2782,17 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -2828,7 +2841,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2843,10 +2856,10 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -2857,10 +2870,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2868,33 +2881,33 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
       </c>
@@ -2918,13 +2931,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -2942,13 +2955,13 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
@@ -2957,13 +2970,13 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>79</v>
@@ -2971,10 +2984,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2982,31 +2995,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3032,13 +3045,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3056,13 +3069,13 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
@@ -3071,13 +3084,13 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
@@ -3085,10 +3098,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3099,7 +3112,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -3108,18 +3121,20 @@
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3144,13 +3159,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>113</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3168,13 +3183,13 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
@@ -3183,13 +3198,13 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>79</v>
@@ -3197,10 +3212,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3208,7 +3223,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3223,17 +3238,15 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3258,13 +3271,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3282,10 +3295,10 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -3297,13 +3310,13 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -3311,10 +3324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3337,15 +3350,17 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3370,13 +3385,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3394,7 +3409,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3409,24 +3424,24 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3434,7 +3449,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3449,13 +3464,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3506,10 +3521,10 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -3521,24 +3536,24 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3561,17 +3576,15 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -3620,7 +3633,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3635,13 +3648,13 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>79</v>
@@ -3649,10 +3662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3675,15 +3688,17 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -3732,7 +3747,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3747,13 +3762,13 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -3761,10 +3776,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3784,16 +3799,16 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3844,7 +3859,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3862,10 +3877,10 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -3873,10 +3888,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3887,7 +3902,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
@@ -3899,17 +3914,15 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>251</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -3958,13 +3971,13 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
@@ -3976,10 +3989,10 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -3987,10 +4000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4013,16 +4026,16 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4048,13 +4061,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4072,7 +4085,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4087,13 +4100,13 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>79</v>
@@ -4101,10 +4114,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4127,16 +4140,16 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4162,13 +4175,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4186,7 +4199,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4201,13 +4214,13 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>79</v>
@@ -4215,10 +4228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4241,15 +4254,17 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4298,7 +4313,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4313,13 +4328,13 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
@@ -4327,10 +4342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4353,17 +4368,15 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>279</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -4412,7 +4425,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4427,15 +4440,129 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN28" t="s" s="2">
+      <c r="L29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>79</v>
       </c>
     </row>
